--- a/data/current.xlsx
+++ b/data/current.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4620" yWindow="2040" windowWidth="21600" windowHeight="11295" tabRatio="685" firstSheet="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="685" firstSheet="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="감가상각액" sheetId="1" state="visible" r:id="rId1"/>
@@ -440,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="83">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -1381,67 +1381,49 @@
         <color auto="1"/>
       </left>
       <right/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1450,45 +1432,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1502,27 +1447,95 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1531,8 +1544,21 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1562,7 +1588,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="347">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2379,64 +2405,94 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2445,26 +2501,20 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2478,82 +2528,76 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2913,22 +2957,22 @@
   <dimension ref="B4:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="2.5" customWidth="1" style="331" min="1" max="1"/>
-    <col width="39.875" customWidth="1" style="331" min="2" max="2"/>
-    <col width="16.625" bestFit="1" customWidth="1" style="332" min="3" max="3"/>
-    <col width="16.25" bestFit="1" customWidth="1" style="275" min="4" max="4"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="331" min="5" max="5"/>
-    <col width="36.125" customWidth="1" style="331" min="6" max="6"/>
+    <col width="2.5" customWidth="1" style="337" min="1" max="1"/>
+    <col width="39.875" customWidth="1" style="337" min="2" max="2"/>
+    <col width="16.625" bestFit="1" customWidth="1" style="338" min="3" max="3"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="333" min="4" max="4"/>
+    <col width="16.5" bestFit="1" customWidth="1" style="337" min="5" max="5"/>
+    <col width="36.125" customWidth="1" style="337" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="3" ht="17.25" customHeight="1" s="331" thickBot="1"/>
-    <row r="4" ht="29.25" customHeight="1" s="331" thickBot="1">
+    <row r="3" ht="17.25" customHeight="1" s="337" thickBot="1"/>
+    <row r="4" ht="29.25" customHeight="1" s="337" thickBot="1">
       <c r="B4" s="254" t="inlineStr">
         <is>
           <t>항목명</t>
         </is>
       </c>
-      <c r="C4" s="333" t="inlineStr">
+      <c r="C4" s="339" t="inlineStr">
         <is>
           <t>총 금액</t>
         </is>
@@ -2949,13 +2993,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" s="331" thickTop="1">
-      <c r="B5" s="334" t="inlineStr">
+    <row r="5" ht="36" customHeight="1" s="337" thickTop="1">
+      <c r="B5" s="340" t="inlineStr">
         <is>
           <t>SP PID SYSTEM</t>
         </is>
       </c>
-      <c r="C5" s="335" t="n">
+      <c r="C5" s="341" t="n">
         <v>77623000</v>
       </c>
       <c r="D5" s="253" t="inlineStr">
@@ -2963,22 +3007,22 @@
           <t>2024.02~2029.01</t>
         </is>
       </c>
-      <c r="E5" s="335" t="n">
+      <c r="E5" s="341" t="n">
         <v>1293716.666666667</v>
       </c>
-      <c r="F5" s="336" t="inlineStr">
+      <c r="F5" s="342" t="inlineStr">
         <is>
           <t>AD 서버,  SP 서버, SPD S/W 구매</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" s="331">
-      <c r="B6" s="337" t="inlineStr">
+    <row r="6" ht="36" customHeight="1" s="337">
+      <c r="B6" s="343" t="inlineStr">
         <is>
           <t>3D Model Support Library</t>
         </is>
       </c>
-      <c r="C6" s="338" t="n">
+      <c r="C6" s="344" t="n">
         <v>396250000</v>
       </c>
       <c r="D6" s="249" t="inlineStr">
@@ -2986,22 +3030,22 @@
           <t>2025.01~2029.12</t>
         </is>
       </c>
-      <c r="E6" s="338" t="n">
+      <c r="E6" s="344" t="n">
         <v>6604166.666666667</v>
       </c>
-      <c r="F6" s="339" t="inlineStr">
+      <c r="F6" s="345" t="inlineStr">
         <is>
           <t>E3D, S3D</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" s="331">
-      <c r="B7" s="337" t="inlineStr">
+    <row r="7" ht="36" customHeight="1" s="337">
+      <c r="B7" s="343" t="inlineStr">
         <is>
           <t>문서관리시스템(e-Central)</t>
         </is>
       </c>
-      <c r="C7" s="338" t="n">
+      <c r="C7" s="344" t="n">
         <v>323000000</v>
       </c>
       <c r="D7" s="249" t="inlineStr">
@@ -3009,23 +3053,23 @@
           <t>2024.04~2029.03</t>
         </is>
       </c>
-      <c r="E7" s="338" t="n">
+      <c r="E7" s="344" t="n">
         <v>5383333.333333333</v>
       </c>
-      <c r="F7" s="340" t="inlineStr">
+      <c r="F7" s="346" t="inlineStr">
         <is>
           <t>인피니솔루션(라이선스, 시스템 구축)
 도프텍(시스템 구축, 서버)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="49.5" customHeight="1" s="331">
-      <c r="B8" s="341" t="inlineStr">
+    <row r="8" ht="49.5" customHeight="1" s="337">
+      <c r="B8" s="347" t="inlineStr">
         <is>
           <t>[배관 설계 관리 시스템] 3D IT SYSTEM</t>
         </is>
       </c>
-      <c r="C8" s="342" t="n">
+      <c r="C8" s="348" t="n">
         <v>648761300</v>
       </c>
       <c r="D8" s="251" t="inlineStr">
@@ -3033,10 +3077,10 @@
           <t>2025.04~2030.03</t>
         </is>
       </c>
-      <c r="E8" s="338" t="n">
+      <c r="E8" s="344" t="n">
         <v>10812688.33333333</v>
       </c>
-      <c r="F8" s="340" t="inlineStr">
+      <c r="F8" s="346" t="inlineStr">
         <is>
           <t>3D Clash Report (E3D,S3D)
  e-Sketch (E3D)
@@ -3044,13 +3088,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" s="331">
-      <c r="B9" s="337" t="inlineStr">
+    <row r="9" ht="36" customHeight="1" s="337">
+      <c r="B9" s="343" t="inlineStr">
         <is>
           <t>e-STRESS</t>
         </is>
       </c>
-      <c r="C9" s="338" t="n">
+      <c r="C9" s="344" t="n">
         <v>151736125</v>
       </c>
       <c r="D9" s="249" t="inlineStr">
@@ -3058,18 +3102,18 @@
           <t>2024.11~2029.10</t>
         </is>
       </c>
-      <c r="E9" s="338" t="n">
+      <c r="E9" s="344" t="n">
         <v>2528935.416666667</v>
       </c>
-      <c r="F9" s="339" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="331">
-      <c r="B10" s="337" t="inlineStr">
+      <c r="F9" s="345" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="337">
+      <c r="B10" s="343" t="inlineStr">
         <is>
           <t>[배관 공사 관리 시스템] e-CONSTRICTION</t>
         </is>
       </c>
-      <c r="C10" s="338" t="n">
+      <c r="C10" s="344" t="n">
         <v>855000000</v>
       </c>
       <c r="D10" s="249" t="inlineStr">
@@ -3077,22 +3121,22 @@
           <t>2025.08~2030.07</t>
         </is>
       </c>
-      <c r="E10" s="338" t="n">
+      <c r="E10" s="344" t="n">
         <v>14250000</v>
       </c>
-      <c r="F10" s="339" t="inlineStr">
+      <c r="F10" s="345" t="inlineStr">
         <is>
           <t>Piping Welding, Material</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1" s="331">
-      <c r="B11" s="337" t="inlineStr">
+    <row r="11" ht="36" customHeight="1" s="337">
+      <c r="B11" s="343" t="inlineStr">
         <is>
           <t>ePMCS Plus</t>
         </is>
       </c>
-      <c r="C11" s="338" t="n">
+      <c r="C11" s="344" t="n">
         <v>700000000</v>
       </c>
       <c r="D11" s="249" t="inlineStr">
@@ -3100,18 +3144,18 @@
           <t>2026.06~2031.05</t>
         </is>
       </c>
-      <c r="E11" s="338" t="n">
+      <c r="E11" s="344" t="n">
         <v>11666666.66666667</v>
       </c>
-      <c r="F11" s="339" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1" s="331">
-      <c r="B12" s="337" t="inlineStr">
+      <c r="F11" s="345" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="337">
+      <c r="B12" s="343" t="inlineStr">
         <is>
           <t>Agentic AI</t>
         </is>
       </c>
-      <c r="C12" s="338" t="n">
+      <c r="C12" s="344" t="n">
         <v>180000000</v>
       </c>
       <c r="D12" s="249" t="inlineStr">
@@ -3119,18 +3163,18 @@
           <t>2026.10~2031.09</t>
         </is>
       </c>
-      <c r="E12" s="338" t="n">
+      <c r="E12" s="344" t="n">
         <v>3000000</v>
       </c>
-      <c r="F12" s="339" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1" s="331">
-      <c r="B13" s="337" t="inlineStr">
+      <c r="F12" s="345" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="337">
+      <c r="B13" s="343" t="inlineStr">
         <is>
           <t>배관 Support Program</t>
         </is>
       </c>
-      <c r="C13" s="338" t="n">
+      <c r="C13" s="344" t="n">
         <v>190000000</v>
       </c>
       <c r="D13" s="249" t="inlineStr">
@@ -3138,22 +3182,22 @@
           <t>2026.12~2031.11</t>
         </is>
       </c>
-      <c r="E13" s="338" t="n">
+      <c r="E13" s="344" t="n">
         <v>3166666.666666667</v>
       </c>
-      <c r="F13" s="339" t="inlineStr">
+      <c r="F13" s="345" t="inlineStr">
         <is>
           <t>S3D Only</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1" s="331">
-      <c r="B14" s="337" t="inlineStr">
+    <row r="14" ht="36" customHeight="1" s="337">
+      <c r="B14" s="343" t="inlineStr">
         <is>
           <t>e-WCS (2D)</t>
         </is>
       </c>
-      <c r="C14" s="338" t="n">
+      <c r="C14" s="344" t="n">
         <v>200000000</v>
       </c>
       <c r="D14" s="249" t="inlineStr">
@@ -3161,18 +3205,18 @@
           <t>2026.12~2031.11</t>
         </is>
       </c>
-      <c r="E14" s="338" t="n">
+      <c r="E14" s="344" t="n">
         <v>3333333.333333333</v>
       </c>
-      <c r="F14" s="339" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" s="331">
-      <c r="B15" s="337" t="inlineStr">
+      <c r="F14" s="345" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="337">
+      <c r="B15" s="343" t="inlineStr">
         <is>
           <t>FMCS 분리</t>
         </is>
       </c>
-      <c r="C15" s="338" t="n">
+      <c r="C15" s="344" t="n">
         <v>50000000</v>
       </c>
       <c r="D15" s="249" t="inlineStr">
@@ -3180,22 +3224,22 @@
           <t>2026.05~2031.04</t>
         </is>
       </c>
-      <c r="E15" s="338" t="n">
+      <c r="E15" s="344" t="n">
         <v>833333.3333333334</v>
       </c>
-      <c r="F15" s="339" t="inlineStr">
+      <c r="F15" s="345" t="inlineStr">
         <is>
           <t>e-WCS(3D), PWMS, PMS, FMCS 분리</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" s="331">
-      <c r="B16" s="337" t="inlineStr">
+    <row r="16" ht="36" customHeight="1" s="337">
+      <c r="B16" s="343" t="inlineStr">
         <is>
           <t>토목설계 Program 영구 구매</t>
         </is>
       </c>
-      <c r="C16" s="338" t="n">
+      <c r="C16" s="344" t="n">
         <v>6100000</v>
       </c>
       <c r="D16" s="249" t="inlineStr">
@@ -3203,22 +3247,22 @@
           <t>2026.04~2031.03</t>
         </is>
       </c>
-      <c r="E16" s="338" t="n">
+      <c r="E16" s="344" t="n">
         <v>101666.6666666667</v>
       </c>
-      <c r="F16" s="339" t="inlineStr">
+      <c r="F16" s="345" t="inlineStr">
         <is>
           <t>L Pile, Group Pile</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1" s="331">
-      <c r="B17" s="337" t="inlineStr">
+    <row r="17" ht="36" customHeight="1" s="337">
+      <c r="B17" s="343" t="inlineStr">
         <is>
           <t>SmartPlant Foundation User</t>
         </is>
       </c>
-      <c r="C17" s="338" t="n">
+      <c r="C17" s="344" t="n">
         <v>25000000</v>
       </c>
       <c r="D17" s="249" t="inlineStr">
@@ -3226,18 +3270,18 @@
           <t>2026.01~2030.12</t>
         </is>
       </c>
-      <c r="E17" s="338" t="n">
+      <c r="E17" s="344" t="n">
         <v>416666.6666666667</v>
       </c>
-      <c r="F17" s="339" t="n"/>
-    </row>
-    <row r="18" ht="36" customHeight="1" s="331">
-      <c r="B18" s="337" t="inlineStr">
+      <c r="F17" s="345" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="337">
+      <c r="B18" s="343" t="inlineStr">
         <is>
           <t>Smart 3D Upgrade</t>
         </is>
       </c>
-      <c r="C18" s="338" t="n">
+      <c r="C18" s="344" t="n">
         <v>182000000</v>
       </c>
       <c r="D18" s="249" t="inlineStr">
@@ -3245,18 +3289,18 @@
           <t>2026.01~2030.12</t>
         </is>
       </c>
-      <c r="E18" s="338" t="n">
+      <c r="E18" s="344" t="n">
         <v>3033333.333333333</v>
       </c>
-      <c r="F18" s="339" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1" s="331">
-      <c r="B19" s="337" t="inlineStr">
+      <c r="F18" s="345" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="337">
+      <c r="B19" s="343" t="inlineStr">
         <is>
           <t>3D Model Server</t>
         </is>
       </c>
-      <c r="C19" s="338" t="n">
+      <c r="C19" s="344" t="n">
         <v>50000000</v>
       </c>
       <c r="D19" s="249" t="inlineStr">
@@ -3264,22 +3308,22 @@
           <t>2026.01~2030.12</t>
         </is>
       </c>
-      <c r="E19" s="338" t="n">
+      <c r="E19" s="344" t="n">
         <v>833333.3333333334</v>
       </c>
-      <c r="F19" s="339" t="inlineStr">
+      <c r="F19" s="345" t="inlineStr">
         <is>
           <t>노후 서버 교체</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1" s="331">
-      <c r="B20" s="337" t="inlineStr">
+    <row r="20" ht="36" customHeight="1" s="337">
+      <c r="B20" s="343" t="inlineStr">
         <is>
           <t>e-PMCS Plus 운영 서버</t>
         </is>
       </c>
-      <c r="C20" s="338" t="n">
+      <c r="C20" s="344" t="n">
         <v>50000000</v>
       </c>
       <c r="D20" s="249" t="inlineStr">
@@ -3287,18 +3331,18 @@
           <t>2026.01~2030.12</t>
         </is>
       </c>
-      <c r="E20" s="338" t="n">
+      <c r="E20" s="344" t="n">
         <v>833333.3333333334</v>
       </c>
-      <c r="F20" s="339" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1" s="331">
-      <c r="B21" s="337" t="inlineStr">
+      <c r="F20" s="345" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="337">
+      <c r="B21" s="343" t="inlineStr">
         <is>
           <t>SPI Server</t>
         </is>
       </c>
-      <c r="C21" s="338" t="n">
+      <c r="C21" s="344" t="n">
         <v>37600000</v>
       </c>
       <c r="D21" s="249" t="inlineStr">
@@ -3306,22 +3350,22 @@
           <t>2026.01~2030.12</t>
         </is>
       </c>
-      <c r="E21" s="338" t="n">
+      <c r="E21" s="344" t="n">
         <v>626666.6666666666</v>
       </c>
-      <c r="F21" s="339" t="inlineStr">
+      <c r="F21" s="345" t="inlineStr">
         <is>
           <t>노후 서버 교체</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1" s="331" thickBot="1">
-      <c r="B22" s="343" t="inlineStr">
+    <row r="22" ht="36" customHeight="1" s="337" thickBot="1">
+      <c r="B22" s="349" t="inlineStr">
         <is>
           <t>Smart Instrumentation</t>
         </is>
       </c>
-      <c r="C22" s="344" t="n">
+      <c r="C22" s="350" t="n">
         <v>42326000</v>
       </c>
       <c r="D22" s="259" t="inlineStr">
@@ -3329,22 +3373,22 @@
           <t>2026.01~2030.12</t>
         </is>
       </c>
-      <c r="E22" s="344" t="n">
+      <c r="E22" s="350" t="n">
         <v>705433.3333333334</v>
       </c>
-      <c r="F22" s="345" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" s="331" thickBot="1" thickTop="1">
+      <c r="F22" s="351" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="337" thickBot="1" thickTop="1">
       <c r="B23" s="260" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C23" s="346" t="n">
+      <c r="C23" s="352" t="n">
         <v>4165396425</v>
       </c>
       <c r="D23" s="262" t="n"/>
-      <c r="E23" s="346" t="n">
+      <c r="E23" s="352" t="n">
         <v>69423273.75</v>
       </c>
       <c r="F23" s="263" t="n"/>
@@ -3360,24 +3404,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B4:E27"/>
+  <dimension ref="A4:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="2.5" customWidth="1" style="331" min="1" max="1"/>
-    <col width="39.875" customWidth="1" style="331" min="2" max="2"/>
-    <col width="16.625" bestFit="1" customWidth="1" style="332" min="3" max="3"/>
-    <col width="33" bestFit="1" customWidth="1" style="275" min="4" max="4"/>
-    <col width="35" bestFit="1" customWidth="1" style="331" min="5" max="5"/>
+    <col width="2.5" customWidth="1" style="337" min="1" max="1"/>
+    <col width="39.875" customWidth="1" style="337" min="2" max="2"/>
+    <col width="16.625" bestFit="1" customWidth="1" style="338" min="3" max="3"/>
+    <col width="33" bestFit="1" customWidth="1" style="333" min="4" max="4"/>
+    <col width="20" bestFit="1" customWidth="1" style="333" min="5" max="5"/>
+    <col width="35" bestFit="1" customWidth="1" style="337" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="3" ht="17.25" customHeight="1" s="331" thickBot="1"/>
-    <row r="4" ht="29.25" customHeight="1" s="331" thickBot="1">
+    <row r="3" ht="17.25" customHeight="1" s="337" thickBot="1"/>
+    <row r="4" ht="29.25" customHeight="1" s="337" thickBot="1">
       <c r="B4" s="254" t="inlineStr">
         <is>
           <t>항목명</t>
         </is>
       </c>
-      <c r="C4" s="333" t="inlineStr">
+      <c r="C4" s="339" t="inlineStr">
         <is>
           <t>총 금액</t>
         </is>
@@ -3387,35 +3432,45 @@
           <t>계약 기간</t>
         </is>
       </c>
-      <c r="E4" s="257" t="inlineStr">
+      <c r="E4" s="273" t="inlineStr">
+        <is>
+          <t>지출 월</t>
+        </is>
+      </c>
+      <c r="F4" s="257" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" s="331" thickTop="1">
-      <c r="B5" s="334" t="inlineStr">
+    <row r="5" ht="36" customHeight="1" s="337" thickTop="1">
+      <c r="B5" s="340" t="inlineStr">
         <is>
           <t>PDS, SmartPlant계열 유지보수료</t>
         </is>
       </c>
-      <c r="C5" s="335" t="n">
+      <c r="C5" s="341" t="n">
         <v>160000000</v>
       </c>
-      <c r="D5" s="253" t="inlineStr">
+      <c r="D5" s="272" t="inlineStr">
         <is>
           <t>2026.04.01~2027.03.31</t>
         </is>
       </c>
-      <c r="E5" s="336" t="n"/>
-    </row>
-    <row r="6" ht="36" customHeight="1" s="331">
-      <c r="B6" s="337" t="inlineStr">
+      <c r="E5" s="274" t="inlineStr">
+        <is>
+          <t>매년 4월 1회</t>
+        </is>
+      </c>
+      <c r="F5" s="342" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="337">
+      <c r="B6" s="343" t="inlineStr">
         <is>
           <t>AVEVA E3D 12 Copies Lease (1년)</t>
         </is>
       </c>
-      <c r="C6" s="338" t="n">
+      <c r="C6" s="344" t="n">
         <v>37000000</v>
       </c>
       <c r="D6" s="249" t="inlineStr">
@@ -3423,15 +3478,20 @@
           <t>2026.01.01~2026.12.31</t>
         </is>
       </c>
-      <c r="E6" s="339" t="n"/>
-    </row>
-    <row r="7" ht="36" customHeight="1" s="331">
-      <c r="B7" s="341" t="inlineStr">
+      <c r="E6" s="275" t="inlineStr">
+        <is>
+          <t>매년 1월 1회</t>
+        </is>
+      </c>
+      <c r="F6" s="345" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="337">
+      <c r="B7" s="347" t="inlineStr">
         <is>
           <t>3D Model Physical Support Library 사용료</t>
         </is>
       </c>
-      <c r="C7" s="342" t="n">
+      <c r="C7" s="348" t="n">
         <v>40000000</v>
       </c>
       <c r="D7" s="251" t="inlineStr">
@@ -3439,15 +3499,20 @@
           <t>2026.02.01~2027.01.30</t>
         </is>
       </c>
-      <c r="E7" s="340" t="n"/>
-    </row>
-    <row r="8" ht="36" customHeight="1" s="331">
-      <c r="B8" s="337" t="inlineStr">
+      <c r="E7" s="276" t="inlineStr">
+        <is>
+          <t>매년 2월 1회</t>
+        </is>
+      </c>
+      <c r="F7" s="346" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="337">
+      <c r="B8" s="343" t="inlineStr">
         <is>
           <t>배관설계관리시스템(S-GEN)</t>
         </is>
       </c>
-      <c r="C8" s="338" t="n">
+      <c r="C8" s="344" t="n">
         <v>23000000</v>
       </c>
       <c r="D8" s="249" t="inlineStr">
@@ -3455,19 +3520,24 @@
           <t>2026.07.01~2027.06.30</t>
         </is>
       </c>
-      <c r="E8" s="339" t="inlineStr">
+      <c r="E8" s="275" t="inlineStr">
+        <is>
+          <t>매년 7월 1회</t>
+        </is>
+      </c>
+      <c r="F8" s="345" t="inlineStr">
         <is>
           <t>자동 연장 계약</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" s="331">
-      <c r="B9" s="337" t="inlineStr">
+    <row r="9" ht="36" customHeight="1" s="337">
+      <c r="B9" s="343" t="inlineStr">
         <is>
           <t>배관설계관리시스템 유지보수</t>
         </is>
       </c>
-      <c r="C9" s="338" t="n">
+      <c r="C9" s="344" t="n">
         <v>115000000</v>
       </c>
       <c r="D9" s="249" t="inlineStr">
@@ -3475,19 +3545,24 @@
           <t>2026.02.01~2027.01.30</t>
         </is>
       </c>
-      <c r="E9" s="339" t="inlineStr">
+      <c r="E9" s="276" t="inlineStr">
+        <is>
+          <t>매년 2월 1회</t>
+        </is>
+      </c>
+      <c r="F9" s="345" t="inlineStr">
         <is>
           <t>3D Quality Check</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" s="331">
-      <c r="B10" s="337" t="inlineStr">
+    <row r="10" ht="36" customHeight="1" s="337">
+      <c r="B10" s="343" t="inlineStr">
         <is>
           <t>배관공사관리시스템 유지보수</t>
         </is>
       </c>
-      <c r="C10" s="338" t="n">
+      <c r="C10" s="344" t="n">
         <v>145000000</v>
       </c>
       <c r="D10" s="249" t="inlineStr">
@@ -3495,35 +3570,41 @@
           <t>2026.02.01~2027.01.30</t>
         </is>
       </c>
-      <c r="E10" s="339" t="inlineStr">
+      <c r="E10" s="276" t="inlineStr">
+        <is>
+          <t>매년 2월 1회</t>
+        </is>
+      </c>
+      <c r="F10" s="345" t="inlineStr">
         <is>
           <t>e-CONSTRUCTION</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1" s="331">
-      <c r="B11" s="337" t="inlineStr">
+    <row r="11" ht="36" customHeight="1" s="337">
+      <c r="B11" s="343" t="inlineStr">
         <is>
           <t>ePMCS Plus 추가 개발</t>
         </is>
       </c>
-      <c r="C11" s="338" t="n">
+      <c r="C11" s="344" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="249" t="n"/>
-      <c r="E11" s="339" t="inlineStr">
+      <c r="E11" s="275" t="n"/>
+      <c r="F11" s="345" t="inlineStr">
         <is>
           <t>개발 일정 미정</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" s="331">
-      <c r="B12" s="337" t="inlineStr">
+    <row r="12" ht="36" customHeight="1" s="337">
+      <c r="B12" s="343" t="inlineStr">
         <is>
           <t>ETAP (전기 전력해석 프로그램)</t>
         </is>
       </c>
-      <c r="C12" s="338" t="n">
+      <c r="C12" s="344" t="n">
         <v>14000000</v>
       </c>
       <c r="D12" s="249" t="inlineStr">
@@ -3531,15 +3612,20 @@
           <t>2026.03.01~2027.02.28</t>
         </is>
       </c>
-      <c r="E12" s="339" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1" s="331">
-      <c r="B13" s="337" t="inlineStr">
+      <c r="E12" s="275" t="inlineStr">
+        <is>
+          <t>매년 3월 1회</t>
+        </is>
+      </c>
+      <c r="F12" s="345" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="337">
+      <c r="B13" s="343" t="inlineStr">
         <is>
           <t>CHEMCAD CC-Steady State</t>
         </is>
       </c>
-      <c r="C13" s="338" t="n">
+      <c r="C13" s="344" t="n">
         <v>32000000</v>
       </c>
       <c r="D13" s="249" t="inlineStr">
@@ -3547,15 +3633,20 @@
           <t>2026.03.05~2027.03.04</t>
         </is>
       </c>
-      <c r="E13" s="339" t="n"/>
-    </row>
-    <row r="14" ht="36" customHeight="1" s="331">
-      <c r="B14" s="337" t="inlineStr">
+      <c r="E13" s="275" t="inlineStr">
+        <is>
+          <t>매년 3월 1회</t>
+        </is>
+      </c>
+      <c r="F13" s="345" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="337">
+      <c r="B14" s="343" t="inlineStr">
         <is>
           <t>LinkMeMine 원격S/W 유지보수(15Copy)</t>
         </is>
       </c>
-      <c r="C14" s="338" t="n">
+      <c r="C14" s="344" t="n">
         <v>1000000</v>
       </c>
       <c r="D14" s="249" t="inlineStr">
@@ -3563,15 +3654,20 @@
           <t>2026.04.17~2027.04.16</t>
         </is>
       </c>
-      <c r="E14" s="339" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" s="331">
-      <c r="B15" s="337" t="inlineStr">
+      <c r="E14" s="275" t="inlineStr">
+        <is>
+          <t>매년 4월 1회</t>
+        </is>
+      </c>
+      <c r="F14" s="345" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="337">
+      <c r="B15" s="343" t="inlineStr">
         <is>
           <t>TANK CX (1년)</t>
         </is>
       </c>
-      <c r="C15" s="338" t="n">
+      <c r="C15" s="344" t="n">
         <v>1500000</v>
       </c>
       <c r="D15" s="249" t="inlineStr">
@@ -3579,15 +3675,20 @@
           <t>2026.04.01~2027.03.31</t>
         </is>
       </c>
-      <c r="E15" s="339" t="n"/>
-    </row>
-    <row r="16" ht="36" customHeight="1" s="331">
-      <c r="B16" s="337" t="inlineStr">
+      <c r="E15" s="275" t="inlineStr">
+        <is>
+          <t>매년 4월 1회</t>
+        </is>
+      </c>
+      <c r="F15" s="345" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1" s="337">
+      <c r="B16" s="343" t="inlineStr">
         <is>
           <t>CAESAR II (2copy - 1년)</t>
         </is>
       </c>
-      <c r="C16" s="338" t="n">
+      <c r="C16" s="344" t="n">
         <v>13000000</v>
       </c>
       <c r="D16" s="249" t="inlineStr">
@@ -3595,15 +3696,20 @@
           <t>2026.04.01~2027.03.31</t>
         </is>
       </c>
-      <c r="E16" s="339" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" s="331">
-      <c r="B17" s="337" t="inlineStr">
+      <c r="E16" s="275" t="inlineStr">
+        <is>
+          <t>매년 4월 1회</t>
+        </is>
+      </c>
+      <c r="F16" s="345" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="337">
+      <c r="B17" s="343" t="inlineStr">
         <is>
           <t>MIDAS GEN(Advanced, WEB) (3년)</t>
         </is>
       </c>
-      <c r="C17" s="338" t="n">
+      <c r="C17" s="344" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="249" t="inlineStr">
@@ -3611,19 +3717,24 @@
           <t>2025.06.01~2028.05.31</t>
         </is>
       </c>
-      <c r="E17" s="339" t="inlineStr">
-        <is>
-          <t>2028.06.01 계약 예정 (금액 미정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" s="331">
-      <c r="B18" s="337" t="inlineStr">
+      <c r="E17" s="275" t="inlineStr">
+        <is>
+          <t>2028년 6월 재계약 예정</t>
+        </is>
+      </c>
+      <c r="F17" s="345" t="inlineStr">
+        <is>
+          <t>금액 미정</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="337">
+      <c r="B18" s="343" t="inlineStr">
         <is>
           <t>ASPEN ONE (1년)</t>
         </is>
       </c>
-      <c r="C18" s="338" t="n">
+      <c r="C18" s="344" t="n">
         <v>200000000</v>
       </c>
       <c r="D18" s="249" t="inlineStr">
@@ -3631,15 +3742,20 @@
           <t>2026.09.26~2027.09.25</t>
         </is>
       </c>
-      <c r="E18" s="339" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1" s="331">
-      <c r="B19" s="337" t="inlineStr">
+      <c r="E18" s="275" t="inlineStr">
+        <is>
+          <t>매년 9월 1회</t>
+        </is>
+      </c>
+      <c r="F18" s="345" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="337">
+      <c r="B19" s="343" t="inlineStr">
         <is>
           <t>Compress (1년)</t>
         </is>
       </c>
-      <c r="C19" s="338" t="n">
+      <c r="C19" s="344" t="n">
         <v>14500000</v>
       </c>
       <c r="D19" s="249" t="inlineStr">
@@ -3647,15 +3763,20 @@
           <t>2026.02.10~2027.02.09</t>
         </is>
       </c>
-      <c r="E19" s="339" t="n"/>
-    </row>
-    <row r="20" ht="36" customHeight="1" s="331">
-      <c r="B20" s="337" t="inlineStr">
+      <c r="E19" s="275" t="inlineStr">
+        <is>
+          <t>매년 2월 1회</t>
+        </is>
+      </c>
+      <c r="F19" s="345" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1" s="337">
+      <c r="B20" s="343" t="inlineStr">
         <is>
           <t>Tekla Structure Construction Modeling 유지보수</t>
         </is>
       </c>
-      <c r="C20" s="338" t="n">
+      <c r="C20" s="344" t="n">
         <v>3000000</v>
       </c>
       <c r="D20" s="249" t="inlineStr">
@@ -3663,15 +3784,20 @@
           <t>2026.01.01~2026.12.31</t>
         </is>
       </c>
-      <c r="E20" s="339" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1" s="331">
-      <c r="B21" s="337" t="inlineStr">
+      <c r="E20" s="275" t="inlineStr">
+        <is>
+          <t>매년 1월 1회</t>
+        </is>
+      </c>
+      <c r="F20" s="345" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="337">
+      <c r="B21" s="343" t="inlineStr">
         <is>
           <t>문서관리시스템 유지보수</t>
         </is>
       </c>
-      <c r="C21" s="338" t="n">
+      <c r="C21" s="344" t="n">
         <v>94000000</v>
       </c>
       <c r="D21" s="249" t="inlineStr">
@@ -3679,19 +3805,25 @@
           <t>2026.06.01~2027.05.31</t>
         </is>
       </c>
-      <c r="E21" s="340" t="inlineStr">
+      <c r="E21" s="276" t="inlineStr">
+        <is>
+          <t>매월 5,500,000원씩 +
+매년 28,000,000원씩</t>
+        </is>
+      </c>
+      <c r="F21" s="346" t="inlineStr">
         <is>
           <t>Markus, OpenText, DocuPlace PDM</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1" s="331">
-      <c r="B22" s="337" t="inlineStr">
+    <row r="22" ht="36" customHeight="1" s="337">
+      <c r="B22" s="343" t="inlineStr">
         <is>
           <t>문서관리시스템 운영 관리</t>
         </is>
       </c>
-      <c r="C22" s="338" t="n">
+      <c r="C22" s="344" t="n">
         <v>78000000</v>
       </c>
       <c r="D22" s="249" t="inlineStr">
@@ -3699,15 +3831,20 @@
           <t>2026.01.01~2026.12.31</t>
         </is>
       </c>
-      <c r="E22" s="339" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" s="331">
-      <c r="B23" s="337" t="inlineStr">
+      <c r="E22" s="275" t="inlineStr">
+        <is>
+          <t>매월 6,500,000원씩</t>
+        </is>
+      </c>
+      <c r="F22" s="345" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="337">
+      <c r="B23" s="343" t="inlineStr">
         <is>
           <t>Navisworks Simulate (1년)</t>
         </is>
       </c>
-      <c r="C23" s="338" t="n">
+      <c r="C23" s="344" t="n">
         <v>138000000</v>
       </c>
       <c r="D23" s="249" t="inlineStr">
@@ -3715,15 +3852,24 @@
           <t>2026.03.10 ~ 2027.03.09</t>
         </is>
       </c>
-      <c r="E23" s="339" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1" s="331">
-      <c r="B24" s="337" t="inlineStr">
+      <c r="E23" s="275" t="inlineStr">
+        <is>
+          <t>매월 약 11,000,000원씩</t>
+        </is>
+      </c>
+      <c r="F23" s="345" t="inlineStr">
+        <is>
+          <t>실제 사용량 만큼 지출</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="337">
+      <c r="B24" s="343" t="inlineStr">
         <is>
           <t>Agentic AI(유지보수)</t>
         </is>
       </c>
-      <c r="C24" s="338" t="n">
+      <c r="C24" s="344" t="n">
         <v>100000000</v>
       </c>
       <c r="D24" s="249" t="inlineStr">
@@ -3731,15 +3877,20 @@
           <t>2026.10.30 ~ 2027.10.29</t>
         </is>
       </c>
-      <c r="E24" s="339" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1" s="331">
-      <c r="B25" s="337" t="inlineStr">
+      <c r="E24" s="275" t="inlineStr">
+        <is>
+          <t>매년 10월 1회</t>
+        </is>
+      </c>
+      <c r="F24" s="345" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="337">
+      <c r="B25" s="343" t="inlineStr">
         <is>
           <t>토건 설계 프로그램 (1년)</t>
         </is>
       </c>
-      <c r="C25" s="338" t="n">
+      <c r="C25" s="344" t="n">
         <v>14000000</v>
       </c>
       <c r="D25" s="249" t="inlineStr">
@@ -3747,19 +3898,24 @@
           <t>2026.03~2027.02</t>
         </is>
       </c>
-      <c r="E25" s="339" t="inlineStr">
+      <c r="E25" s="275" t="inlineStr">
+        <is>
+          <t>매년 3월 1회</t>
+        </is>
+      </c>
+      <c r="F25" s="345" t="inlineStr">
         <is>
           <t>IDEA StartiCa, Hilti Profis, Settle3</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1" s="331" thickBot="1">
-      <c r="B26" s="337" t="inlineStr">
+    <row r="26" ht="36" customHeight="1" s="337" thickBot="1">
+      <c r="B26" s="343" t="inlineStr">
         <is>
           <t>벤틀리 STAAD Pro, Microstation V8</t>
         </is>
       </c>
-      <c r="C26" s="338" t="n">
+      <c r="C26" s="344" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="249" t="inlineStr">
@@ -3767,23 +3923,25 @@
           <t>분기</t>
         </is>
       </c>
-      <c r="E26" s="339" t="inlineStr">
+      <c r="E26" s="275" t="n"/>
+      <c r="F26" s="345" t="inlineStr">
         <is>
           <t>LNIC PDH-PP Project 귀속</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1" s="331" thickBot="1" thickTop="1">
+    <row r="27" ht="36" customHeight="1" s="337" thickBot="1" thickTop="1">
       <c r="B27" s="260" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C27" s="346" t="n">
+      <c r="C27" s="352" t="n">
         <v>1223000000</v>
       </c>
       <c r="D27" s="262" t="n"/>
-      <c r="E27" s="263" t="n"/>
+      <c r="E27" s="277" t="n"/>
+      <c r="F27" s="263" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/current.xlsx
+++ b/data/current.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="685" firstSheet="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="685" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="감가상각액" sheetId="1" state="visible" r:id="rId1"/>
@@ -1403,6 +1403,131 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1437,131 +1562,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1">
@@ -2423,6 +2423,159 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2445,159 +2598,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2954,13 +2954,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B4:F23"/>
+  <dimension ref="B4:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="2.5" customWidth="1" style="337" min="1" max="1"/>
     <col width="39.875" customWidth="1" style="337" min="2" max="2"/>
     <col width="16.625" bestFit="1" customWidth="1" style="338" min="3" max="3"/>
-    <col width="16.25" bestFit="1" customWidth="1" style="333" min="4" max="4"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="281" min="4" max="4"/>
     <col width="16.5" bestFit="1" customWidth="1" style="337" min="5" max="5"/>
     <col width="36.125" customWidth="1" style="337" min="6" max="6"/>
   </cols>
@@ -3359,39 +3359,63 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1" s="337" thickBot="1">
-      <c r="B22" s="349" t="inlineStr">
+    <row r="22" ht="36" customHeight="1" s="337">
+      <c r="B22" s="343" t="inlineStr">
         <is>
           <t>Smart Instrumentation</t>
         </is>
       </c>
-      <c r="C22" s="350" t="n">
+      <c r="C22" s="344" t="n">
         <v>42326000</v>
       </c>
-      <c r="D22" s="259" t="inlineStr">
+      <c r="D22" s="249" t="inlineStr">
         <is>
           <t>2026.01~2030.12</t>
         </is>
       </c>
-      <c r="E22" s="350" t="n">
+      <c r="E22" s="344" t="n">
         <v>705433.3333333334</v>
       </c>
-      <c r="F22" s="351" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" s="337" thickBot="1" thickTop="1">
-      <c r="B23" s="260" t="inlineStr">
+      <c r="F22" s="345" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="337" thickBot="1">
+      <c r="B23" s="349" t="inlineStr">
+        <is>
+          <t>3JCNS CAS, E&amp;I</t>
+        </is>
+      </c>
+      <c r="C23" s="350" t="n">
+        <v>760000000</v>
+      </c>
+      <c r="D23" s="259" t="inlineStr">
+        <is>
+          <t>2026.12~2031.11</t>
+        </is>
+      </c>
+      <c r="E23" s="350" t="n">
+        <v>12666666.66666667</v>
+      </c>
+      <c r="F23" s="351" t="inlineStr">
+        <is>
+          <t>AVEVA E3D용
+2026.12~2028.12 LNIC Project 귀속</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="337" thickBot="1" thickTop="1">
+      <c r="B24" s="260" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C23" s="352" t="n">
-        <v>4165396425</v>
-      </c>
-      <c r="D23" s="262" t="n"/>
-      <c r="E23" s="352" t="n">
-        <v>69423273.75</v>
-      </c>
-      <c r="F23" s="263" t="n"/>
+      <c r="C24" s="352" t="n">
+        <v>4925396425</v>
+      </c>
+      <c r="D24" s="262" t="n"/>
+      <c r="E24" s="352" t="n">
+        <v>82089940.41666667</v>
+      </c>
+      <c r="F24" s="263" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3404,15 +3428,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:F27"/>
+  <dimension ref="B4:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="2.5" customWidth="1" style="337" min="1" max="1"/>
     <col width="39.875" customWidth="1" style="337" min="2" max="2"/>
     <col width="16.625" bestFit="1" customWidth="1" style="338" min="3" max="3"/>
-    <col width="33" bestFit="1" customWidth="1" style="333" min="4" max="4"/>
-    <col width="20" bestFit="1" customWidth="1" style="333" min="5" max="5"/>
-    <col width="35" bestFit="1" customWidth="1" style="337" min="6" max="6"/>
+    <col width="33" bestFit="1" customWidth="1" style="281" min="4" max="4"/>
+    <col width="20" bestFit="1" customWidth="1" style="281" min="5" max="5"/>
+    <col width="39.75" customWidth="1" style="337" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="3" ht="17.25" customHeight="1" s="337" thickBot="1"/>
@@ -3584,32 +3608,36 @@
     <row r="11" ht="36" customHeight="1" s="337">
       <c r="B11" s="343" t="inlineStr">
         <is>
-          <t>ePMCS Plus 추가 개발</t>
+          <t>ETAP (전기 전력해석 프로그램)</t>
         </is>
       </c>
       <c r="C11" s="344" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="249" t="n"/>
-      <c r="E11" s="275" t="n"/>
-      <c r="F11" s="345" t="inlineStr">
-        <is>
-          <t>개발 일정 미정</t>
-        </is>
-      </c>
+        <v>14000000</v>
+      </c>
+      <c r="D11" s="249" t="inlineStr">
+        <is>
+          <t>2026.03.01~2027.02.28</t>
+        </is>
+      </c>
+      <c r="E11" s="275" t="inlineStr">
+        <is>
+          <t>매년 3월 1회</t>
+        </is>
+      </c>
+      <c r="F11" s="345" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1" s="337">
       <c r="B12" s="343" t="inlineStr">
         <is>
-          <t>ETAP (전기 전력해석 프로그램)</t>
+          <t>CHEMCAD CC-Steady State</t>
         </is>
       </c>
       <c r="C12" s="344" t="n">
-        <v>14000000</v>
+        <v>32000000</v>
       </c>
       <c r="D12" s="249" t="inlineStr">
         <is>
-          <t>2026.03.01~2027.02.28</t>
+          <t>2026.03.05~2027.03.04</t>
         </is>
       </c>
       <c r="E12" s="275" t="inlineStr">
@@ -3622,20 +3650,20 @@
     <row r="13" ht="36" customHeight="1" s="337">
       <c r="B13" s="343" t="inlineStr">
         <is>
-          <t>CHEMCAD CC-Steady State</t>
+          <t>LinkMeMine 원격S/W 유지보수(15Copy)</t>
         </is>
       </c>
       <c r="C13" s="344" t="n">
-        <v>32000000</v>
+        <v>1000000</v>
       </c>
       <c r="D13" s="249" t="inlineStr">
         <is>
-          <t>2026.03.05~2027.03.04</t>
+          <t>2026.04.17~2027.04.16</t>
         </is>
       </c>
       <c r="E13" s="275" t="inlineStr">
         <is>
-          <t>매년 3월 1회</t>
+          <t>매년 4월 1회</t>
         </is>
       </c>
       <c r="F13" s="345" t="n"/>
@@ -3643,15 +3671,15 @@
     <row r="14" ht="36" customHeight="1" s="337">
       <c r="B14" s="343" t="inlineStr">
         <is>
-          <t>LinkMeMine 원격S/W 유지보수(15Copy)</t>
+          <t>TANK CX (1년)</t>
         </is>
       </c>
       <c r="C14" s="344" t="n">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="D14" s="249" t="inlineStr">
         <is>
-          <t>2026.04.17~2027.04.16</t>
+          <t>2026.04.01~2027.03.31</t>
         </is>
       </c>
       <c r="E14" s="275" t="inlineStr">
@@ -3664,11 +3692,11 @@
     <row r="15" ht="36" customHeight="1" s="337">
       <c r="B15" s="343" t="inlineStr">
         <is>
-          <t>TANK CX (1년)</t>
+          <t>CAESAR II (2copy - 1년)</t>
         </is>
       </c>
       <c r="C15" s="344" t="n">
-        <v>1500000</v>
+        <v>13000000</v>
       </c>
       <c r="D15" s="249" t="inlineStr">
         <is>
@@ -3685,66 +3713,66 @@
     <row r="16" ht="36" customHeight="1" s="337">
       <c r="B16" s="343" t="inlineStr">
         <is>
-          <t>CAESAR II (2copy - 1년)</t>
+          <t>MIDAS GEN(Advanced, WEB) (3년)</t>
         </is>
       </c>
       <c r="C16" s="344" t="n">
-        <v>13000000</v>
+        <v>0</v>
       </c>
       <c r="D16" s="249" t="inlineStr">
         <is>
-          <t>2026.04.01~2027.03.31</t>
+          <t>2025.06.01~2028.05.31</t>
         </is>
       </c>
       <c r="E16" s="275" t="inlineStr">
         <is>
-          <t>매년 4월 1회</t>
-        </is>
-      </c>
-      <c r="F16" s="345" t="n"/>
+          <t>2028년 6월 재계약 예정</t>
+        </is>
+      </c>
+      <c r="F16" s="345" t="inlineStr">
+        <is>
+          <t>금액 미정</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="36" customHeight="1" s="337">
       <c r="B17" s="343" t="inlineStr">
         <is>
-          <t>MIDAS GEN(Advanced, WEB) (3년)</t>
+          <t>ASPEN ONE (1년)</t>
         </is>
       </c>
       <c r="C17" s="344" t="n">
-        <v>0</v>
+        <v>200000000</v>
       </c>
       <c r="D17" s="249" t="inlineStr">
         <is>
-          <t>2025.06.01~2028.05.31</t>
+          <t>2026.09.26~2027.09.25</t>
         </is>
       </c>
       <c r="E17" s="275" t="inlineStr">
         <is>
-          <t>2028년 6월 재계약 예정</t>
-        </is>
-      </c>
-      <c r="F17" s="345" t="inlineStr">
-        <is>
-          <t>금액 미정</t>
-        </is>
-      </c>
+          <t>매년 9월 1회</t>
+        </is>
+      </c>
+      <c r="F17" s="345" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1" s="337">
       <c r="B18" s="343" t="inlineStr">
         <is>
-          <t>ASPEN ONE (1년)</t>
+          <t>Compress (1년)</t>
         </is>
       </c>
       <c r="C18" s="344" t="n">
-        <v>200000000</v>
+        <v>14500000</v>
       </c>
       <c r="D18" s="249" t="inlineStr">
         <is>
-          <t>2026.09.26~2027.09.25</t>
+          <t>2026.02.10~2027.02.09</t>
         </is>
       </c>
       <c r="E18" s="275" t="inlineStr">
         <is>
-          <t>매년 9월 1회</t>
+          <t>매년 2월 1회</t>
         </is>
       </c>
       <c r="F18" s="345" t="n"/>
@@ -3752,20 +3780,20 @@
     <row r="19" ht="36" customHeight="1" s="337">
       <c r="B19" s="343" t="inlineStr">
         <is>
-          <t>Compress (1년)</t>
+          <t>Tekla Structure Construction Modeling 유지보수</t>
         </is>
       </c>
       <c r="C19" s="344" t="n">
-        <v>14500000</v>
+        <v>3000000</v>
       </c>
       <c r="D19" s="249" t="inlineStr">
         <is>
-          <t>2026.02.10~2027.02.09</t>
+          <t>2026.01.01~2026.12.31</t>
         </is>
       </c>
       <c r="E19" s="275" t="inlineStr">
         <is>
-          <t>매년 2월 1회</t>
+          <t>매년 1월 1회</t>
         </is>
       </c>
       <c r="F19" s="345" t="n"/>
@@ -3773,93 +3801,99 @@
     <row r="20" ht="36" customHeight="1" s="337">
       <c r="B20" s="343" t="inlineStr">
         <is>
-          <t>Tekla Structure Construction Modeling 유지보수</t>
+          <t>문서관리시스템 유지보수</t>
         </is>
       </c>
       <c r="C20" s="344" t="n">
-        <v>3000000</v>
+        <v>94000000</v>
       </c>
       <c r="D20" s="249" t="inlineStr">
         <is>
-          <t>2026.01.01~2026.12.31</t>
-        </is>
-      </c>
-      <c r="E20" s="275" t="inlineStr">
-        <is>
-          <t>매년 1월 1회</t>
-        </is>
-      </c>
-      <c r="F20" s="345" t="n"/>
+          <t>2026.06.01~2027.05.31</t>
+        </is>
+      </c>
+      <c r="E20" s="276" t="inlineStr">
+        <is>
+          <t>매월 5,500,000원씩 +
+매년 28,000,000원씩</t>
+        </is>
+      </c>
+      <c r="F20" s="346" t="inlineStr">
+        <is>
+          <t>Markus, OpenText, DocuPlace PDM</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="36" customHeight="1" s="337">
       <c r="B21" s="343" t="inlineStr">
         <is>
-          <t>문서관리시스템 유지보수</t>
+          <t>문서관리시스템 운영 관리</t>
         </is>
       </c>
       <c r="C21" s="344" t="n">
-        <v>94000000</v>
+        <v>78000000</v>
       </c>
       <c r="D21" s="249" t="inlineStr">
         <is>
-          <t>2026.06.01~2027.05.31</t>
-        </is>
-      </c>
-      <c r="E21" s="276" t="inlineStr">
-        <is>
-          <t>매월 5,500,000원씩 +
-매년 28,000,000원씩</t>
-        </is>
-      </c>
-      <c r="F21" s="346" t="inlineStr">
-        <is>
-          <t>Markus, OpenText, DocuPlace PDM</t>
-        </is>
-      </c>
+          <t>2026.01.01~2026.12.31</t>
+        </is>
+      </c>
+      <c r="E21" s="275" t="inlineStr">
+        <is>
+          <t>매월 6,500,000원씩</t>
+        </is>
+      </c>
+      <c r="F21" s="345" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="337">
       <c r="B22" s="343" t="inlineStr">
         <is>
-          <t>문서관리시스템 운영 관리</t>
+          <t>Navisworks Simulate (1년)</t>
         </is>
       </c>
       <c r="C22" s="344" t="n">
-        <v>78000000</v>
+        <v>138000000</v>
       </c>
       <c r="D22" s="249" t="inlineStr">
         <is>
-          <t>2026.01.01~2026.12.31</t>
+          <t>2026.03.10 ~ 2027.03.09</t>
         </is>
       </c>
       <c r="E22" s="275" t="inlineStr">
         <is>
-          <t>매월 6,500,000원씩</t>
-        </is>
-      </c>
-      <c r="F22" s="345" t="n"/>
+          <t>매월 약 11,000,000원씩</t>
+        </is>
+      </c>
+      <c r="F22" s="345" t="inlineStr">
+        <is>
+          <t>실제 사용량 만큼 지출</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="36" customHeight="1" s="337">
       <c r="B23" s="343" t="inlineStr">
         <is>
-          <t>Navisworks Simulate (1년)</t>
+          <t>3JCNS CAS, E&amp;I 유지보수</t>
         </is>
       </c>
       <c r="C23" s="344" t="n">
-        <v>138000000</v>
+        <v>102000000</v>
       </c>
       <c r="D23" s="249" t="inlineStr">
         <is>
-          <t>2026.03.10 ~ 2027.03.09</t>
+          <t>2028.12.01 ~ 2029.11.30</t>
         </is>
       </c>
       <c r="E23" s="275" t="inlineStr">
         <is>
-          <t>매월 약 11,000,000원씩</t>
+          <t>매년 12월 1회</t>
         </is>
       </c>
       <c r="F23" s="345" t="inlineStr">
         <is>
-          <t>실제 사용량 만큼 지출</t>
+          <t>2026년: 첫해 유지보수비 0원
+AVEVA E3D
+2027년 LNIC Project 귀속 (12월 일시납)</t>
         </is>
       </c>
     </row>
@@ -3916,17 +3950,22 @@
         </is>
       </c>
       <c r="C26" s="344" t="n">
-        <v>0</v>
+        <v>64000000</v>
       </c>
       <c r="D26" s="249" t="inlineStr">
         <is>
-          <t>분기</t>
-        </is>
-      </c>
-      <c r="E26" s="275" t="n"/>
+          <t>2026.01~2026.12</t>
+        </is>
+      </c>
+      <c r="E26" s="276" t="inlineStr">
+        <is>
+          <t>1월 4월 7월 10월
+년 4회</t>
+        </is>
+      </c>
       <c r="F26" s="345" t="inlineStr">
         <is>
-          <t>LNIC PDH-PP Project 귀속</t>
+          <t>2026년~2027년 LNIC Project에서 205백만원 리스계약 중</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3976,7 @@
         </is>
       </c>
       <c r="C27" s="352" t="n">
-        <v>1223000000</v>
+        <v>1389000000</v>
       </c>
       <c r="D27" s="262" t="n"/>
       <c r="E27" s="277" t="n"/>
@@ -3945,5 +3984,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/data/current.xlsx
+++ b/data/current.xlsx
@@ -3428,7 +3428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B4:F27"/>
+  <dimension ref="B4:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="2.5" customWidth="1" style="337" min="1" max="1"/>
@@ -3437,6 +3437,8 @@
     <col width="33" bestFit="1" customWidth="1" style="281" min="4" max="4"/>
     <col width="20" bestFit="1" customWidth="1" style="281" min="5" max="5"/>
     <col width="39.75" customWidth="1" style="337" min="6" max="6"/>
+    <col width="16.625" customWidth="1" style="337" min="7" max="7"/>
+    <col width="20" customWidth="1" style="337" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="17.25" customHeight="1" s="337" thickBot="1"/>
@@ -3466,6 +3468,16 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="G4" s="273" t="inlineStr">
+        <is>
+          <t>2026년 금액</t>
+        </is>
+      </c>
+      <c r="H4" s="273" t="inlineStr">
+        <is>
+          <t>2026년 지출 월</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="36" customHeight="1" s="337" thickTop="1">
       <c r="B5" s="340" t="inlineStr">
@@ -3487,6 +3499,14 @@
         </is>
       </c>
       <c r="F5" s="342" t="n"/>
+      <c r="G5" s="341" t="n">
+        <v>121584000</v>
+      </c>
+      <c r="H5" s="274" t="inlineStr">
+        <is>
+          <t>2026년 4월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="36" customHeight="1" s="337">
       <c r="B6" s="343" t="inlineStr">
@@ -3508,6 +3528,14 @@
         </is>
       </c>
       <c r="F6" s="345" t="n"/>
+      <c r="G6" s="344" t="n">
+        <v>36600000</v>
+      </c>
+      <c r="H6" s="275" t="inlineStr">
+        <is>
+          <t>2026년 1월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1" s="337">
       <c r="B7" s="347" t="inlineStr">
@@ -3529,6 +3557,14 @@
         </is>
       </c>
       <c r="F7" s="346" t="n"/>
+      <c r="G7" s="348" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="H7" s="276" t="inlineStr">
+        <is>
+          <t>2026년 2월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="36" customHeight="1" s="337">
       <c r="B8" s="343" t="inlineStr">
@@ -3554,6 +3590,14 @@
           <t>자동 연장 계약</t>
         </is>
       </c>
+      <c r="G8" s="344" t="n">
+        <v>21630000</v>
+      </c>
+      <c r="H8" s="275" t="inlineStr">
+        <is>
+          <t>2026년 7월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="36" customHeight="1" s="337">
       <c r="B9" s="343" t="inlineStr">
@@ -3579,6 +3623,14 @@
           <t>3D Quality Check</t>
         </is>
       </c>
+      <c r="G9" s="344" t="n">
+        <v>109482000</v>
+      </c>
+      <c r="H9" s="276" t="inlineStr">
+        <is>
+          <t>2026년 2월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="36" customHeight="1" s="337">
       <c r="B10" s="343" t="inlineStr">
@@ -3604,6 +3656,14 @@
           <t>e-CONSTRUCTION</t>
         </is>
       </c>
+      <c r="G10" s="344" t="n">
+        <v>135000000</v>
+      </c>
+      <c r="H10" s="276" t="inlineStr">
+        <is>
+          <t>2026년 2월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1" s="337">
       <c r="B11" s="343" t="inlineStr">
@@ -3625,6 +3685,14 @@
         </is>
       </c>
       <c r="F11" s="345" t="n"/>
+      <c r="G11" s="344" t="n">
+        <v>13483000</v>
+      </c>
+      <c r="H11" s="275" t="inlineStr">
+        <is>
+          <t>2026년 3월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="36" customHeight="1" s="337">
       <c r="B12" s="343" t="inlineStr">
@@ -3646,6 +3714,14 @@
         </is>
       </c>
       <c r="F12" s="345" t="n"/>
+      <c r="G12" s="344" t="n">
+        <v>30326000</v>
+      </c>
+      <c r="H12" s="275" t="inlineStr">
+        <is>
+          <t>2026년 3월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="36" customHeight="1" s="337">
       <c r="B13" s="343" t="inlineStr">
@@ -3667,6 +3743,14 @@
         </is>
       </c>
       <c r="F13" s="345" t="n"/>
+      <c r="G13" s="344" t="n">
+        <v>750000</v>
+      </c>
+      <c r="H13" s="275" t="inlineStr">
+        <is>
+          <t>2026년 4월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="36" customHeight="1" s="337">
       <c r="B14" s="343" t="inlineStr">
@@ -3688,6 +3772,14 @@
         </is>
       </c>
       <c r="F14" s="345" t="n"/>
+      <c r="G14" s="344" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="H14" s="275" t="inlineStr">
+        <is>
+          <t>2026년 4월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="36" customHeight="1" s="337">
       <c r="B15" s="343" t="inlineStr">
@@ -3709,6 +3801,14 @@
         </is>
       </c>
       <c r="F15" s="345" t="n"/>
+      <c r="G15" s="344" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="H15" s="275" t="inlineStr">
+        <is>
+          <t>2026년 4월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="36" customHeight="1" s="337">
       <c r="B16" s="343" t="inlineStr">
@@ -3734,6 +3834,16 @@
           <t>금액 미정</t>
         </is>
       </c>
+      <c r="G16" s="344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="275" t="inlineStr">
+        <is>
+          <t>2028년 6월 재계약 예정</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="36" customHeight="1" s="337">
       <c r="B17" s="343" t="inlineStr">
@@ -3755,6 +3865,14 @@
         </is>
       </c>
       <c r="F17" s="345" t="n"/>
+      <c r="G17" s="344" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="H17" s="275" t="inlineStr">
+        <is>
+          <t>2026년 9월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1" s="337">
       <c r="B18" s="343" t="inlineStr">
@@ -3776,6 +3894,14 @@
         </is>
       </c>
       <c r="F18" s="345" t="n"/>
+      <c r="G18" s="344" t="n">
+        <v>13933000</v>
+      </c>
+      <c r="H18" s="275" t="inlineStr">
+        <is>
+          <t>2026년 2월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1" s="337">
       <c r="B19" s="343" t="inlineStr">
@@ -3797,6 +3923,14 @@
         </is>
       </c>
       <c r="F19" s="345" t="n"/>
+      <c r="G19" s="344" t="n">
+        <v>2901000</v>
+      </c>
+      <c r="H19" s="275" t="inlineStr">
+        <is>
+          <t>2026년 1월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="36" customHeight="1" s="337">
       <c r="B20" s="343" t="inlineStr">
@@ -3823,6 +3957,15 @@
           <t>Markus, OpenText, DocuPlace PDM</t>
         </is>
       </c>
+      <c r="G20" s="344" t="n">
+        <v>94000000</v>
+      </c>
+      <c r="H20" s="276" t="inlineStr">
+        <is>
+          <t>매월 5,500,000원씩 +
+6월 28,000,000원</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="36" customHeight="1" s="337">
       <c r="B21" s="343" t="inlineStr">
@@ -3844,6 +3987,14 @@
         </is>
       </c>
       <c r="F21" s="345" t="n"/>
+      <c r="G21" s="344" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="H21" s="275" t="inlineStr">
+        <is>
+          <t>매월 6,500,000원씩</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="36" customHeight="1" s="337">
       <c r="B22" s="343" t="inlineStr">
@@ -3867,6 +4018,14 @@
       <c r="F22" s="345" t="inlineStr">
         <is>
           <t>실제 사용량 만큼 지출</t>
+        </is>
+      </c>
+      <c r="G22" s="344" t="n">
+        <v>132000000</v>
+      </c>
+      <c r="H22" s="275" t="inlineStr">
+        <is>
+          <t>매월 약 11,000,000원씩</t>
         </is>
       </c>
     </row>
@@ -3896,6 +4055,14 @@
 2027년 LNIC Project 귀속 (12월 일시납)</t>
         </is>
       </c>
+      <c r="G23" s="344" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="H23" s="275" t="inlineStr">
+        <is>
+          <t>2026년 12월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1" s="337">
       <c r="B24" s="343" t="inlineStr">
@@ -3917,6 +4084,14 @@
         </is>
       </c>
       <c r="F24" s="345" t="n"/>
+      <c r="G24" s="344" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="H24" s="275" t="inlineStr">
+        <is>
+          <t>2026년 10월 1회</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="36" customHeight="1" s="337">
       <c r="B25" s="343" t="inlineStr">
@@ -3940,6 +4115,14 @@
       <c r="F25" s="345" t="inlineStr">
         <is>
           <t>IDEA StartiCa, Hilti Profis, Settle3</t>
+        </is>
+      </c>
+      <c r="G25" s="344" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="H25" s="275" t="inlineStr">
+        <is>
+          <t>2026년 3월 1회</t>
         </is>
       </c>
     </row>
